--- a/generated/spreadsheet/verbose/planning-permission-for-relevant-demolition-in-a-conservation-area-demolition-con-area-verbose.xlsx
+++ b/generated/spreadsheet/verbose/planning-permission-for-relevant-demolition-in-a-conservation-area-demolition-con-area-verbose.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N109"/>
+  <dimension ref="A1:N108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -642,12 +642,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>application-sub-type</t>
+          <t>planning-authority</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Application sub type</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -656,7 +656,7 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Further classification of the application type for specific variations within the main application type</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -690,12 +690,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>planning-authority</t>
+          <t>submission-date</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Submission date</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -704,12 +704,12 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>Date the application is submitted in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>submission-date</t>
+          <t>modules</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Modules[]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -752,12 +752,12 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>List of required modules for this application that can be used to validate the application</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -786,21 +786,29 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>modules</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
+          <t>Documents[]</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -844,19 +852,19 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>name</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -900,19 +908,19 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>description</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -922,7 +930,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -956,29 +964,29 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>document-types</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1012,24 +1020,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>document-types</t>
+          <t>uploaded-date</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Uploaded date</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1068,29 +1076,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>uploaded-date</t>
+          <t>file</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>base64-content</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Base64</t>
+        </is>
+      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1150,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>base64-content</t>
+          <t>filename</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Base64</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1154,7 +1170,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1198,17 +1214,17 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>filename</t>
+          <t>mime-type</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1218,7 +1234,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1262,22 +1278,22 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>mime-type</t>
+          <t>file-size</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>File size</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1306,37 +1322,29 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>fee</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
+          <t>Fee</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>file-size</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>File size</t>
-        </is>
-      </c>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -1346,7 +1354,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1380,19 +1388,19 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>amount-paid</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1436,75 +1444,67 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>amount-paid</t>
+          <t>transactions</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Transactions[]</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>applicant-contact</t>
+        </is>
+      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Telephone number and email address of the applicant.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>applicant-reference</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>fee</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Fee</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>transactions</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Transactions[]</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1514,21 +1514,13 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>applicant-contact</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Telephone number and email address of the applicant.</t>
@@ -1536,23 +1528,31 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>applicant-reference</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -1586,21 +1586,29 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -1610,7 +1618,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1644,24 +1652,24 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>contact-priority</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -1671,72 +1679,64 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="2" t="n"/>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>applicant-details</t>
+        </is>
+      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Telephone number and email address of the applicant.</t>
+          <t>Name and contact information for the parties making the application.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>applicants</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>Applicants[]</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>contact-priority</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>applicant-details</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Name and contact information for the parties making the application.</t>
@@ -1754,21 +1754,29 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -1778,7 +1786,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1812,19 +1820,19 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -1834,7 +1842,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1868,19 +1876,19 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -1924,19 +1932,19 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -1980,19 +1988,19 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2002,53 +2010,45 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n"/>
-      <c r="B29" s="2" t="n"/>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>agent-contact</t>
+        </is>
+      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information for the parties making the application.</t>
+          <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>applicants</t>
+          <t>agent-reference</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2058,21 +2058,13 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>agent-contact</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="2" t="n"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -2080,23 +2072,31 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>agent-reference</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -2130,21 +2130,29 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -2154,7 +2162,7 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2188,24 +2196,24 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>contact-priority</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2215,8 +2223,16 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n"/>
-      <c r="B33" s="2" t="n"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>agent-details</t>
+        </is>
+      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -2224,63 +2240,47 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>contact-priority</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>agent-details</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="2" t="n"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -2298,21 +2298,29 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -2322,7 +2330,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2356,19 +2364,19 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -2378,7 +2386,7 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2412,19 +2420,19 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -2468,19 +2476,19 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -2524,19 +2532,19 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -2546,7 +2554,7 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2570,29 +2578,21 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>company</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>user-role</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>User role</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
@@ -2640,12 +2640,12 @@
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -2655,64 +2655,56 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="2" t="n"/>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity net gain</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>bng</t>
+        </is>
+      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information if an agent is being used.</t>
+          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>bng-condition-applies</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>user-role</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>User role</t>
-        </is>
-      </c>
+          <t>Biodiversity gain condition applies</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity net gain</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>bng</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>How any natural habitats on the development site will be improved by the proposed works.</t>
@@ -2720,28 +2712,36 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>bng-condition-applies</t>
+          <t>bng-condition-exemption-reasons</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition applies</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
+          <t>Biodiversity gain condition exemption reason[]</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>exemption-type</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Exemption type</t>
+        </is>
+      </c>
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
+          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -2770,12 +2770,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>exemption-type</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Exemption type</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
@@ -2784,12 +2784,12 @@
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
+          <t>The reason the exemption applies to this proposal</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -2808,22 +2808,22 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>bng-condition-exemption-reasons</t>
+          <t>bng-details</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition exemption reason[]</t>
+          <t>Biodiversity net gain details</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>pre-development-date</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Pre development date</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
@@ -2832,12 +2832,12 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>The reason the exemption applies to this proposal</t>
+          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>pre-development-date</t>
+          <t>pre-development-biodiversity-value</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Pre development date</t>
+          <t>Pre development biodiversity value</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
@@ -2880,12 +2880,12 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
+          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -2914,12 +2914,12 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>pre-development-biodiversity-value</t>
+          <t>earlier-date-reason</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Pre development biodiversity value</t>
+          <t>Earlier date reason</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -2928,17 +2928,17 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
+          <t>Reason for using a pre-development date that is earlier than the application submission</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2962,12 +2962,12 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>earlier-date-reason</t>
+          <t>habitat-loss-after-2020</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Earlier date reason</t>
+          <t>Habitat loss after 2020</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -2976,12 +2976,12 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Reason for using a pre-development date that is earlier than the application submission</t>
+          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3010,31 +3010,39 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>habitat-loss-after-2020</t>
+          <t>habitat-loss-details</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss after 2020</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr"/>
+          <t>Habitat loss details</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>loss-date</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Loss date</t>
+        </is>
+      </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
+          <t>Date the activity causing habitat loss or degradation occurred</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3068,24 +3076,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>loss-date</t>
+          <t>pre-loss-biodiversity-value</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Loss date</t>
+          <t>Pre loss biodiversity value</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Date the activity causing habitat loss or degradation occurred</t>
+          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -3124,29 +3132,29 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>pre-loss-biodiversity-value</t>
+          <t>supporting-evidence</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Pre loss biodiversity value</t>
+          <t>Supporting evidence</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
+          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3170,39 +3178,31 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>habitat-loss-details</t>
+          <t>metric-publication-date</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss details</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>supporting-evidence</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>Supporting evidence</t>
-        </is>
-      </c>
+          <t>Metric publication date</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
+          <t>Publication date of the biodiversity metric tool used for calculations</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3226,12 +3226,12 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>metric-publication-date</t>
+          <t>irreplaceable-habitats</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Metric publication date</t>
+          <t>Irreplaceable habitats</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
@@ -3240,12 +3240,12 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Publication date of the biodiversity metric tool used for calculations</t>
+          <t>Indicates whether the site contains any irreplaceable habitats</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>irreplaceable-habitats</t>
+          <t>irreplaceable-habitats-details</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats</t>
+          <t>Irreplaceable habitats details</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
@@ -3288,17 +3288,17 @@
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether the site contains any irreplaceable habitats</t>
+          <t>Description and references for any irreplaceable habitats identified on the site</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3322,21 +3322,29 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>irreplaceable-habitats-details</t>
+          <t>supporting-documents</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats details</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Description and references for any irreplaceable habitats identified on the site</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -3346,53 +3354,45 @@
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n"/>
-      <c r="B55" s="2" t="n"/>
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>checklist</t>
+        </is>
+      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>bng-details</t>
+          <t>national-req-types</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity net gain details</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>supporting-documents</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>National requirement types[]</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -3409,27 +3409,27 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Checklist</t>
+          <t>Community consultation</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>checklist</t>
+          <t>community-consultation</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>What community consultation activities have taken place as part of the application</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>national-req-types</t>
+          <t>have-consulted</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
+          <t>Have consulted</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
@@ -3440,12 +3440,12 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Whether community consultation has been carried out</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -3455,16 +3455,8 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>Community consultation</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>community-consultation</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="n"/>
+      <c r="B57" s="2" t="n"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>What community consultation activities have taken place as part of the application</t>
@@ -3472,12 +3464,12 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>have-consulted</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Have consulted</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
@@ -3488,36 +3480,44 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Whether community consultation has been carried out</t>
+          <t>Provide details of the community consultation</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n"/>
-      <c r="B58" s="2" t="n"/>
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>conflict-of-interest</t>
+        </is>
+      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>What community consultation activities have taken place as part of the application</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>conflict-to-declare</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
@@ -3528,31 +3528,23 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Provide details of the community consultation</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>conflict-of-interest</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="n"/>
+      <c r="B59" s="2" t="n"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
@@ -3560,12 +3552,12 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>conflict-to-declare</t>
+          <t>conflict-person-name</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>Conflict person name</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
@@ -3576,17 +3568,17 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3600,12 +3592,12 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>conflict-person-name</t>
+          <t>conflict-details</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
@@ -3616,7 +3608,7 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -3631,21 +3623,29 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n"/>
-      <c r="B61" s="2" t="n"/>
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>declaration</t>
+        </is>
+      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>conflict-details</t>
+          <t>name</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
@@ -3656,7 +3656,7 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>A name of a person</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -3666,21 +3666,13 @@
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>declaration</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="n"/>
+      <c r="B62" s="2" t="n"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>Signed and dated verification of the application's accuracy.</t>
@@ -3688,12 +3680,12 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr"/>
@@ -3704,12 +3696,12 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -3728,12 +3720,12 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr"/>
@@ -3744,12 +3736,12 @@
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -3759,21 +3751,29 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n"/>
-      <c r="B64" s="2" t="n"/>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Demolition reason</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>demolition-reason</t>
+        </is>
+      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Why demolition is necessary at the development site</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr"/>
@@ -3784,7 +3784,7 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Why is it necessary to demolish all or part of the building(s) and structure(s)?</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
@@ -3801,27 +3801,27 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Demolition reason</t>
+          <t>Ownership certificates and agricultural land declaration</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>demolition-reason</t>
+          <t>ownership-certs</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Why demolition is necessary at the development site</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>sole-owner</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Sole owner</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
@@ -3832,12 +3832,12 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Why is it necessary to demolish all or part of the building(s) and structure(s)?</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -3847,16 +3847,8 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>ownership-certs</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="n"/>
+      <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
@@ -3864,12 +3856,12 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>sole-owner</t>
+          <t>agricultural-tenants</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
+          <t>Agricultural tenants</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
@@ -3880,7 +3872,7 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>Are there any agricultural tenants on the land?</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -3904,33 +3896,49 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>agricultural-tenants</t>
+          <t>owners-and-tenants</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Agricultural tenants</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr"/>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr"/>
-      <c r="I67" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Are there any agricultural tenants on the land?</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3964,19 +3972,19 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -3986,7 +3994,7 @@
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4020,19 +4028,19 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -4076,19 +4084,19 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -4132,19 +4140,19 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -4154,7 +4162,7 @@
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4178,34 +4186,26 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>notice-date</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Notice date</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -4224,36 +4224,28 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>owners-and-tenants</t>
+          <t>steps-taken</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>notice-date</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>Notice date</t>
-        </is>
-      </c>
+          <t>Steps taken</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -4272,23 +4264,31 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>steps-taken</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr"/>
-      <c r="G74" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>newspaper-name</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>newspaper-name</t>
+          <t>publication-date</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Newspaper name</t>
+          <t>Publication date</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
@@ -4336,12 +4336,12 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -4360,41 +4360,33 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>ownership-cert-option</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>publication-date</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4408,12 +4400,12 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>ownership-cert-option</t>
+          <t>applicant-signature</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
+          <t>Applicant signature</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
@@ -4424,12 +4416,12 @@
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Digital signature of the applicant</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -4448,12 +4440,12 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>applicant-signature</t>
+          <t>agent-signature</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Applicant signature</t>
+          <t>Agent signature</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
@@ -4464,7 +4456,7 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the applicant</t>
+          <t>Digital signature of the agent (if applicable)</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -4488,12 +4480,12 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>agent-signature</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Agent signature</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
@@ -4504,7 +4496,7 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the agent (if applicable)</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -4519,21 +4511,29 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n"/>
-      <c r="B80" s="2" t="n"/>
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>pre-app-advice</t>
+        </is>
+      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>advice-sought</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
@@ -4544,31 +4544,23 @@
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>pre-app-advice</t>
-        </is>
-      </c>
+      <c r="A81" s="2" t="n"/>
+      <c r="B81" s="2" t="n"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>Details of pre-application advice previously received from the planning authority</t>
@@ -4576,12 +4568,12 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>advice-sought</t>
+          <t>officer-name</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr"/>
@@ -4592,17 +4584,17 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4616,12 +4608,12 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>officer-name</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
@@ -4632,7 +4624,7 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -4656,12 +4648,12 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>advice-date</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr"/>
@@ -4672,7 +4664,7 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
@@ -4696,12 +4688,12 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>advice-date</t>
+          <t>advice-summary</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr"/>
@@ -4712,7 +4704,7 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -4727,21 +4719,29 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n"/>
-      <c r="B85" s="2" t="n"/>
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>proposal-details</t>
+        </is>
+      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>advice-summary</t>
+          <t>proposal-description</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Proposal description</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr"/>
@@ -4752,7 +4752,7 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -4762,21 +4762,13 @@
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>proposal-details</t>
-        </is>
-      </c>
+      <c r="A86" s="2" t="n"/>
+      <c r="B86" s="2" t="n"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>What development, works or change of use is proposed</t>
@@ -4784,12 +4776,12 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>proposal-description</t>
+          <t>proposal-started</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
@@ -4800,12 +4792,12 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -4824,12 +4816,12 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>proposal-started</t>
+          <t>proposal-started-date</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
@@ -4840,17 +4832,17 @@
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4864,12 +4856,12 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>proposal-started-date</t>
+          <t>proposal-completed</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Proposal completed</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr"/>
@@ -4880,17 +4872,17 @@
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4904,12 +4896,12 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed</t>
+          <t>proposal-completed-date</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal completion date</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr"/>
@@ -4920,36 +4912,44 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n"/>
-      <c r="B90" s="2" t="n"/>
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Related applications</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>related-applications</t>
+        </is>
+      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>What development, works or change of use is proposed</t>
+          <t>Details of any other development proposals made for the site</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed-date</t>
+          <t>has-related-applications</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>Has related applications</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
@@ -4960,60 +4960,60 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Are there any related applications, previous proposals or demolitions for the site</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>Related applications</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="A91" s="2" t="n"/>
+      <c r="B91" s="2" t="n"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Details of any other development proposals made for the site</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>related-applications</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Details of any other development proposals made for the site</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>has-related-applications</t>
-        </is>
-      </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Has related applications</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr"/>
-      <c r="G91" s="2" t="inlineStr"/>
+          <t>Related applications[]</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H91" s="2" t="inlineStr"/>
       <c r="I91" s="2" t="inlineStr"/>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>Are there any related applications, previous proposals or demolitions for the site</t>
+          <t>The reference for the related application</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -5042,12 +5042,12 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr"/>
@@ -5056,7 +5056,7 @@
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>The reference for the related application</t>
+          <t>A description of the related application</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>decision-date</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Decision date</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr"/>
@@ -5104,7 +5104,7 @@
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>A description of the related application</t>
+          <t>The date when the decision was made, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
@@ -5114,36 +5114,44 @@
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n"/>
-      <c r="B94" s="2" t="n"/>
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Details of any other development proposals made for the site</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>related-applications</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Related applications[]</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>decision-date</t>
+          <t>site-boundary</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Decision date</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr"/>
@@ -5152,12 +5160,12 @@
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>The date when the decision was made, in YYYY-MM-DD format</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -5167,16 +5175,8 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A95" s="2" t="n"/>
+      <c r="B95" s="2" t="n"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -5194,12 +5194,12 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>site-boundary</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr"/>
@@ -5208,12 +5208,12 @@
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr"/>
@@ -5256,7 +5256,7 @@
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>easting</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr"/>
@@ -5304,12 +5304,12 @@
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>easting</t>
+          <t>northing</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr"/>
@@ -5352,7 +5352,7 @@
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
@@ -5386,12 +5386,12 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr"/>
@@ -5400,7 +5400,7 @@
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr"/>
@@ -5448,7 +5448,7 @@
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr"/>
@@ -5496,12 +5496,12 @@
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>uprns</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>UPRNs[]</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr"/>
@@ -5544,7 +5544,7 @@
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
@@ -5559,64 +5559,56 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n"/>
-      <c r="B103" s="2" t="n"/>
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>site-visit</t>
+        </is>
+      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Information to help the planning authority arrange a site visit</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>can-be-seen-from</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>uprns</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>UPRNs[]</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr"/>
       <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>site-visit</t>
-        </is>
-      </c>
+      <c r="A104" s="2" t="n"/>
+      <c r="B104" s="2" t="n"/>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>Information to help the planning authority arrange a site visit</t>
@@ -5624,12 +5616,12 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>can-be-seen-from</t>
+          <t>contact-type</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr"/>
@@ -5640,12 +5632,12 @@
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -5664,12 +5656,12 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>contact-type</t>
+          <t>contact-reference</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Contact reference</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr"/>
@@ -5680,17 +5672,17 @@
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5704,23 +5696,31 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>contact-reference</t>
+          <t>other-contact</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr"/>
-      <c r="G106" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>fullname</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="H106" s="2" t="inlineStr"/>
       <c r="I106" s="2" t="inlineStr"/>
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>fullname</t>
+          <t>number</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr"/>
@@ -5768,7 +5768,7 @@
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr"/>
@@ -5816,7 +5816,7 @@
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
@@ -5825,54 +5825,6 @@
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="n"/>
-      <c r="B109" s="2" t="n"/>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>other-contact</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr"/>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
-      <c r="K109" s="2" t="inlineStr"/>
-      <c r="L109" s="2" t="inlineStr">
-        <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
-        </is>
-      </c>
-      <c r="M109" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N109" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -5880,40 +5832,40 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="B65"/>
-    <mergeCell ref="A34:A41"/>
-    <mergeCell ref="A42:A55"/>
-    <mergeCell ref="A24:A29"/>
-    <mergeCell ref="A2:A19"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A95:A103"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="A66:A80"/>
-    <mergeCell ref="A81:A85"/>
-    <mergeCell ref="B95:B103"/>
-    <mergeCell ref="B59:B61"/>
-    <mergeCell ref="B62:B64"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="B56"/>
-    <mergeCell ref="A91:A94"/>
-    <mergeCell ref="A65"/>
-    <mergeCell ref="B81:B85"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="A104:A109"/>
-    <mergeCell ref="B24:B29"/>
-    <mergeCell ref="A56"/>
-    <mergeCell ref="B86:B90"/>
-    <mergeCell ref="B34:B41"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B42:B55"/>
-    <mergeCell ref="B66:B80"/>
-    <mergeCell ref="B2:B19"/>
-    <mergeCell ref="B91:B94"/>
-    <mergeCell ref="A86:A90"/>
-    <mergeCell ref="B104:B109"/>
+    <mergeCell ref="B64"/>
+    <mergeCell ref="B55"/>
+    <mergeCell ref="A85:A89"/>
+    <mergeCell ref="A103:A108"/>
+    <mergeCell ref="B2:B18"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="A58:A60"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="A65:A79"/>
+    <mergeCell ref="A64"/>
+    <mergeCell ref="B29:B32"/>
+    <mergeCell ref="B41:B54"/>
+    <mergeCell ref="B80:B84"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="B85:B89"/>
+    <mergeCell ref="B23:B28"/>
+    <mergeCell ref="B65:B79"/>
+    <mergeCell ref="A2:A18"/>
+    <mergeCell ref="B103:B108"/>
+    <mergeCell ref="B94:B102"/>
+    <mergeCell ref="A29:A32"/>
+    <mergeCell ref="A33:A40"/>
+    <mergeCell ref="A61:A63"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="A23:A28"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="A94:A102"/>
+    <mergeCell ref="A55"/>
+    <mergeCell ref="A41:A54"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="B33:B40"/>
+    <mergeCell ref="A80:A84"/>
+    <mergeCell ref="B90:B93"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/verbose/planning-permission-for-relevant-demolition-in-a-conservation-area-demolition-con-area-verbose.xlsx
+++ b/generated/spreadsheet/verbose/planning-permission-for-relevant-demolition-in-a-conservation-area-demolition-con-area-verbose.xlsx
@@ -5109,7 +5109,7 @@
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">

--- a/generated/spreadsheet/verbose/planning-permission-for-relevant-demolition-in-a-conservation-area-demolition-con-area-verbose.xlsx
+++ b/generated/spreadsheet/verbose/planning-permission-for-relevant-demolition-in-a-conservation-area-demolition-con-area-verbose.xlsx
@@ -3741,7 +3741,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>proposal-description</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">

--- a/generated/spreadsheet/verbose/planning-permission-for-relevant-demolition-in-a-conservation-area-demolition-con-area-verbose.xlsx
+++ b/generated/spreadsheet/verbose/planning-permission-for-relevant-demolition-in-a-conservation-area-demolition-con-area-verbose.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N108"/>
+  <dimension ref="A1:N109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -442,7 +442,7 @@
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="72" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -521,37 +521,37 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>submission-reference</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Submission reference</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -560,7 +560,7 @@
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A unique reference for the submission</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -579,17 +579,17 @@
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -627,27 +627,27 @@
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>planning-authority</t>
+          <t>specification-profile</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Specification profile</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -656,7 +656,7 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>The specification profile used to determine context-specific allowed codelist values for the application</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -675,27 +675,27 @@
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>submission-date</t>
+          <t>planning-authority</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -704,12 +704,12 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -723,27 +723,27 @@
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>modules</t>
+          <t>submitted-at</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
+          <t>Submitted at</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -752,12 +752,12 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>The date and time the application was submitted</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -771,49 +771,41 @@
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>created-at</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Created at</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The date and time the submission payload was created</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -827,17 +819,17 @@
       <c r="B8" s="2" t="n"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -852,19 +844,19 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -883,17 +875,17 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -908,19 +900,19 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>name</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -930,7 +922,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -939,17 +931,17 @@
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -964,29 +956,29 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>document-types</t>
+          <t>description</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -995,17 +987,17 @@
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1020,24 +1012,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>uploaded-date</t>
+          <t>document-types</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1051,17 +1043,17 @@
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1076,37 +1068,29 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>uploaded-date</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>base64-content</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Base64</t>
-        </is>
-      </c>
+          <t>Uploaded date</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1115,17 +1099,17 @@
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1150,17 +1134,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>filename</t>
+          <t>base64-content</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>Base64</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1170,7 +1154,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1179,17 +1163,17 @@
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1214,17 +1198,17 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>mime-type</t>
+          <t>filename</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1234,7 +1218,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1227,17 @@
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1278,22 +1262,22 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>file-size</t>
+          <t>mime-type</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>File size</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1307,54 +1291,62 @@
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>fee</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Fee</t>
+          <t>Documents[]</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>file</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>file-size</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>File size</t>
+        </is>
+      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1363,17 +1355,17 @@
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1388,24 +1380,24 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>amount-paid</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1419,17 +1411,17 @@
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1444,67 +1436,75 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>transactions</t>
+          <t>amount-paid</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Transactions[]</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>applicant-contact</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Telephone number and email address of the applicant.</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>applicant-reference</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
+          <t>Submission details</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>fee</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Fee</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>transactions</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Transactions[]</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1514,13 +1514,21 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>applicant-contact</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Telephone number and email address of the applicant.</t>
@@ -1528,31 +1536,23 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>applicant-reference</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -1586,29 +1586,21 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -1618,7 +1610,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1652,24 +1644,24 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>contact-priority</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -1679,64 +1671,72 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>applicant-details</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information for the parties making the application.</t>
+          <t>Telephone number and email address of the applicant.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>applicants</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>contact-priority</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n"/>
-      <c r="B24" s="2" t="n"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>applicant-details</t>
+        </is>
+      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Name and contact information for the parties making the application.</t>
@@ -1754,29 +1754,21 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -1786,7 +1778,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1820,19 +1812,19 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -1842,7 +1834,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1876,19 +1868,19 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -1932,19 +1924,19 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -1988,19 +1980,19 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2010,45 +2002,53 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>agent-contact</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="2" t="n"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information if an agent is being used.</t>
+          <t>Name and contact information for the parties making the application.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>agent-reference</t>
+          <t>applicants</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2058,13 +2058,21 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n"/>
-      <c r="B30" s="2" t="n"/>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>agent-contact</t>
+        </is>
+      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -2072,31 +2080,23 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>agent-reference</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2130,29 +2130,21 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -2162,7 +2154,7 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2196,24 +2188,24 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>contact-priority</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2223,16 +2215,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>agent-details</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="n"/>
+      <c r="B33" s="2" t="n"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -2240,47 +2224,63 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>contact-priority</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n"/>
-      <c r="B34" s="2" t="n"/>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>agent-details</t>
+        </is>
+      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -2298,29 +2298,21 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -2330,7 +2322,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2364,19 +2356,19 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -2386,7 +2378,7 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2420,19 +2412,19 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -2476,19 +2468,19 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -2532,19 +2524,19 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -2554,7 +2546,7 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2578,21 +2570,29 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>user-role</t>
+          <t>company</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
@@ -2640,12 +2640,12 @@
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -2655,56 +2655,64 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity net gain</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>bng</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="n"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
+          <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>bng-condition-applies</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition applies</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>user-role</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n"/>
-      <c r="B42" s="2" t="n"/>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity net gain</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>bng</t>
+        </is>
+      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>How any natural habitats on the development site will be improved by the proposed works.</t>
@@ -2712,36 +2720,28 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>bng-condition-exemption-reasons</t>
+          <t>bng-condition-applies</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition exemption reason[]</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>exemption-type</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Exemption type</t>
-        </is>
-      </c>
+          <t>Biodiversity gain condition applies</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
+          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -2770,12 +2770,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>exemption-type</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Exemption type</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
@@ -2784,12 +2784,12 @@
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>The reason the exemption applies to this proposal</t>
+          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -2808,22 +2808,22 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>bng-details</t>
+          <t>bng-condition-exemption-reasons</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity net gain details</t>
+          <t>Biodiversity gain condition exemption reason[]</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>pre-development-date</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Pre development date</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
@@ -2832,12 +2832,12 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
+          <t>The reason the exemption applies to this proposal</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>pre-development-biodiversity-value</t>
+          <t>pre-development-date</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Pre development biodiversity value</t>
+          <t>Pre development date</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
@@ -2880,12 +2880,12 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
+          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -2914,12 +2914,12 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>earlier-date-reason</t>
+          <t>pre-development-biodiversity-value</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Earlier date reason</t>
+          <t>Pre development biodiversity value</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -2928,17 +2928,17 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Reason for using a pre-development date that is earlier than the application submission</t>
+          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2962,12 +2962,12 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>habitat-loss-after-2020</t>
+          <t>earlier-date-reason</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss after 2020</t>
+          <t>Earlier date reason</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -2976,12 +2976,12 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
+          <t>Reason for using a pre-development date that is earlier than the application submission</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3010,39 +3010,31 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>habitat-loss-details</t>
+          <t>habitat-loss-after-2020</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss details</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>loss-date</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>Loss date</t>
-        </is>
-      </c>
+          <t>Habitat loss after 2020</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Date the activity causing habitat loss or degradation occurred</t>
+          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3076,24 +3068,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>pre-loss-biodiversity-value</t>
+          <t>loss-date</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Pre loss biodiversity value</t>
+          <t>Loss date</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
+          <t>Date the activity causing habitat loss or degradation occurred</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -3132,29 +3124,29 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>supporting-evidence</t>
+          <t>pre-loss-biodiversity-value</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Supporting evidence</t>
+          <t>Pre loss biodiversity value</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
+          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3178,31 +3170,39 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>metric-publication-date</t>
+          <t>habitat-loss-details</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Metric publication date</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr"/>
-      <c r="I51" s="2" t="inlineStr"/>
+          <t>Habitat loss details</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>supporting-evidence</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Supporting evidence</t>
+        </is>
+      </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Publication date of the biodiversity metric tool used for calculations</t>
+          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3226,12 +3226,12 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>irreplaceable-habitats</t>
+          <t>metric-publication-date</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats</t>
+          <t>Metric publication date</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
@@ -3240,12 +3240,12 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether the site contains any irreplaceable habitats</t>
+          <t>Publication date of the biodiversity metric tool used for calculations</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>irreplaceable-habitats-details</t>
+          <t>irreplaceable-habitats</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats details</t>
+          <t>Irreplaceable habitats</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
@@ -3288,17 +3288,17 @@
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Description and references for any irreplaceable habitats identified on the site</t>
+          <t>Indicates whether the site contains any irreplaceable habitats</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3322,29 +3322,21 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>irreplaceable-habitats-details</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Irreplaceable habitats details</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Description and references for any irreplaceable habitats identified on the site</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -3354,45 +3346,53 @@
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>checklist</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="n"/>
+      <c r="B55" s="2" t="n"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>national-req-types</t>
+          <t>bng-details</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr"/>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr"/>
-      <c r="I55" s="2" t="inlineStr"/>
+          <t>Biodiversity net gain details</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>supporting-documents</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -3409,27 +3409,27 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Community consultation</t>
+          <t>Checklist</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>community-consultation</t>
+          <t>checklist</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>What community consultation activities have taken place as part of the application</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>have-consulted</t>
+          <t>national-req-types</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Have consulted</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
@@ -3440,12 +3440,12 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Whether community consultation has been carried out</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -3455,8 +3455,16 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n"/>
-      <c r="B57" s="2" t="n"/>
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Community consultation</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>community-consultation</t>
+        </is>
+      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>What community consultation activities have taken place as part of the application</t>
@@ -3464,12 +3472,12 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>have-consulted</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Have consulted</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
@@ -3480,44 +3488,36 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Provide details of the community consultation</t>
+          <t>Whether community consultation has been carried out</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>conflict-of-interest</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="n"/>
+      <c r="B58" s="2" t="n"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>What community consultation activities have taken place as part of the application</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>conflict-to-declare</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
@@ -3528,23 +3528,31 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Provide details of the community consultation</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n"/>
-      <c r="B59" s="2" t="n"/>
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>conflict-of-interest</t>
+        </is>
+      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
@@ -3552,12 +3560,12 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>conflict-person-name</t>
+          <t>conflict-to-declare</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
@@ -3568,17 +3576,17 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3592,12 +3600,12 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>conflict-details</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
@@ -3608,7 +3616,7 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -3623,29 +3631,21 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>declaration</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="n"/>
+      <c r="B61" s="2" t="n"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>conflict-details</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
@@ -3656,7 +3656,7 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -3666,13 +3666,21 @@
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n"/>
-      <c r="B62" s="2" t="n"/>
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>declaration</t>
+        </is>
+      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>Signed and dated verification of the application's accuracy.</t>
@@ -3680,12 +3688,12 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr"/>
@@ -3696,12 +3704,12 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -3720,12 +3728,12 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr"/>
@@ -3736,12 +3744,12 @@
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -3751,29 +3759,21 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>Demolition reason</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>demolition-reason</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="n"/>
+      <c r="B64" s="2" t="n"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Why demolition is necessary at the development site</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr"/>
@@ -3784,12 +3784,12 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Why is it necessary to demolish all or part of the building(s) and structure(s)?</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -3801,27 +3801,27 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificates and agricultural land declaration</t>
+          <t>Demolition reason</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>ownership-certs</t>
+          <t>demolition-reason</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Why demolition is necessary at the development site</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>sole-owner</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
@@ -3832,12 +3832,12 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>Why is it necessary to demolish all or part of the building(s) and structure(s)?</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -3847,8 +3847,16 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n"/>
-      <c r="B66" s="2" t="n"/>
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>ownership-certs</t>
+        </is>
+      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
@@ -3856,12 +3864,12 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>agricultural-tenants</t>
+          <t>sole-owner</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Agricultural tenants</t>
+          <t>Sole owner</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
@@ -3872,7 +3880,7 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Are there any agricultural tenants on the land?</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -3896,49 +3904,33 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>owners-and-tenants</t>
+          <t>agricultural-tenants</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Agricultural tenants</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>Are there any agricultural tenants on the land?</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3972,19 +3964,19 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -3994,7 +3986,7 @@
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4028,19 +4020,19 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -4084,19 +4076,19 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -4140,19 +4132,19 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -4162,7 +4154,7 @@
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4186,26 +4178,34 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>notice-date</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Notice date</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr"/>
-      <c r="I72" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -4224,28 +4224,36 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>steps-taken</t>
+          <t>owners-and-tenants</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr"/>
-      <c r="G73" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>notice-served-date</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Notice served date</t>
+        </is>
+      </c>
       <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -4264,41 +4272,33 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>ownership-cert-option</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>newspaper-name</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>Newspaper name</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4312,41 +4312,33 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>steps-taken</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>publication-date</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Steps taken</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="2" t="inlineStr"/>
       <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4360,33 +4352,41 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>ownership-cert-option</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr"/>
-      <c r="G76" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>newspaper-name</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4400,33 +4400,41 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>applicant-signature</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Applicant signature</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr"/>
-      <c r="G77" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>publication-date</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Publication date</t>
+        </is>
+      </c>
       <c r="H77" s="2" t="inlineStr"/>
       <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the applicant</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4440,12 +4448,12 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>agent-signature</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Agent signature</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
@@ -4456,7 +4464,7 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the agent (if applicable)</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -4466,7 +4474,7 @@
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4488,12 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
@@ -4496,44 +4504,36 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>pre-app-advice</t>
-        </is>
-      </c>
+      <c r="A80" s="2" t="n"/>
+      <c r="B80" s="2" t="n"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>advice-sought</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
@@ -4544,12 +4544,12 @@
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -4559,8 +4559,16 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n"/>
-      <c r="B81" s="2" t="n"/>
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>pre-app-advice</t>
+        </is>
+      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>Details of pre-application advice previously received from the planning authority</t>
@@ -4568,12 +4576,12 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>officer-name</t>
+          <t>advice-sought</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr"/>
@@ -4584,17 +4592,17 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4608,12 +4616,12 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>officer-name</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
@@ -4624,7 +4632,7 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -4648,12 +4656,12 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>advice-date</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr"/>
@@ -4664,12 +4672,12 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -4688,12 +4696,12 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>advice-summary</t>
+          <t>advice-date</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr"/>
@@ -4704,12 +4712,12 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -4719,29 +4727,21 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>proposal-details</t>
-        </is>
-      </c>
+      <c r="A85" s="2" t="n"/>
+      <c r="B85" s="2" t="n"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>What development, works or change of use is proposed</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>advice-summary</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr"/>
@@ -4752,7 +4752,7 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -4762,13 +4762,21 @@
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n"/>
-      <c r="B86" s="2" t="n"/>
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>proposal-details</t>
+        </is>
+      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>What development, works or change of use is proposed</t>
@@ -4776,12 +4784,12 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>proposal-started</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
+          <t>Proposal description</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
@@ -4792,12 +4800,12 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -4816,12 +4824,12 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>proposal-started-date</t>
+          <t>proposal-started</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
@@ -4832,17 +4840,17 @@
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4856,12 +4864,12 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed</t>
+          <t>proposal-started-date</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr"/>
@@ -4872,17 +4880,17 @@
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4896,12 +4904,12 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed-date</t>
+          <t>proposal-completed</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>Proposal completed</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr"/>
@@ -4912,44 +4920,36 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>Related applications</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>related-applications</t>
-        </is>
-      </c>
+      <c r="A90" s="2" t="n"/>
+      <c r="B90" s="2" t="n"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Details of any other development proposals made for the site</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>has-related-applications</t>
+          <t>proposal-completed-date</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Has related applications</t>
+          <t>Proposal completion date</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
@@ -4960,23 +4960,31 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>Are there any related applications, previous proposals or demolitions for the site</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n"/>
-      <c r="B91" s="2" t="n"/>
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Related applications</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>related-applications</t>
+        </is>
+      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>Details of any other development proposals made for the site</t>
@@ -4984,36 +4992,28 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>related-applications</t>
+          <t>has-related-applications</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Related applications[]</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Has related applications</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr"/>
       <c r="I91" s="2" t="inlineStr"/>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>The reference for the related application</t>
+          <t>Are there any related applications, previous proposals or demolitions for the site</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -5042,12 +5042,12 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr"/>
@@ -5056,7 +5056,7 @@
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>A description of the related application</t>
+          <t>The reference for the related application</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>decision-date</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Decision date</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr"/>
@@ -5104,54 +5104,46 @@
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>The date when the decision was made, in YYYY-MM-DD format</t>
+          <t>A description of the related application</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A94" s="2" t="n"/>
+      <c r="B94" s="2" t="n"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of any other development proposals made for the site</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>related-applications</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Related applications[]</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>site-boundary</t>
+          <t>decision-date</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Decision date</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr"/>
@@ -5160,12 +5152,12 @@
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>The date when the decision was made, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -5175,8 +5167,16 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n"/>
-      <c r="B95" s="2" t="n"/>
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -5194,12 +5194,12 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>site-boundary</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr"/>
@@ -5208,12 +5208,12 @@
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr"/>
@@ -5256,7 +5256,7 @@
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>easting</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr"/>
@@ -5304,12 +5304,12 @@
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>easting</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr"/>
@@ -5352,12 +5352,12 @@
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -5386,12 +5386,12 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>northing</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr"/>
@@ -5400,12 +5400,12 @@
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr"/>
@@ -5448,12 +5448,12 @@
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr"/>
@@ -5496,12 +5496,12 @@
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>uprns</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr"/>
@@ -5544,7 +5544,7 @@
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>A text description providing details about the subject.</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
@@ -5559,56 +5559,64 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>site-visit</t>
-        </is>
-      </c>
+      <c r="A103" s="2" t="n"/>
+      <c r="B103" s="2" t="n"/>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>can-be-seen-from</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr"/>
-      <c r="G103" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>uprns</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="H103" s="2" t="inlineStr"/>
       <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n"/>
-      <c r="B104" s="2" t="n"/>
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>site-visit</t>
+        </is>
+      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>Information to help the planning authority arrange a site visit</t>
@@ -5616,12 +5624,12 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>contact-type</t>
+          <t>can-be-seen-from</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Site seen from public area</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr"/>
@@ -5632,12 +5640,12 @@
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -5656,12 +5664,12 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>contact-reference</t>
+          <t>contact-type</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr"/>
@@ -5672,17 +5680,17 @@
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5696,31 +5704,23 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>contact-reference</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>fullname</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>Full name</t>
-        </is>
-      </c>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr"/>
       <c r="I106" s="2" t="inlineStr"/>
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>fullname</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Full name</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr"/>
@@ -5768,7 +5768,7 @@
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>number</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr"/>
@@ -5816,15 +5816,63 @@
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
+          <t>A phone number</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n"/>
+      <c r="B109" s="2" t="n"/>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>other-contact</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr"/>
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
           <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
-      <c r="M108" s="2" t="inlineStr">
+      <c r="M109" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N108" s="2" t="inlineStr">
+      <c r="N109" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -5832,40 +5880,40 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="B64"/>
-    <mergeCell ref="B55"/>
-    <mergeCell ref="A85:A89"/>
-    <mergeCell ref="A103:A108"/>
-    <mergeCell ref="B2:B18"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="A58:A60"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="A65:A79"/>
-    <mergeCell ref="A64"/>
-    <mergeCell ref="B29:B32"/>
-    <mergeCell ref="B41:B54"/>
-    <mergeCell ref="B80:B84"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="B85:B89"/>
-    <mergeCell ref="B23:B28"/>
-    <mergeCell ref="B65:B79"/>
-    <mergeCell ref="A2:A18"/>
-    <mergeCell ref="B103:B108"/>
-    <mergeCell ref="B94:B102"/>
-    <mergeCell ref="A29:A32"/>
-    <mergeCell ref="A33:A40"/>
-    <mergeCell ref="A61:A63"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="A23:A28"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="A94:A102"/>
-    <mergeCell ref="A55"/>
-    <mergeCell ref="A41:A54"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="B33:B40"/>
-    <mergeCell ref="A80:A84"/>
-    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="B65"/>
+    <mergeCell ref="A34:A41"/>
+    <mergeCell ref="A42:A55"/>
+    <mergeCell ref="A24:A29"/>
+    <mergeCell ref="A2:A19"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A95:A103"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="A66:A80"/>
+    <mergeCell ref="A81:A85"/>
+    <mergeCell ref="B95:B103"/>
+    <mergeCell ref="B59:B61"/>
+    <mergeCell ref="B62:B64"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="B56"/>
+    <mergeCell ref="A91:A94"/>
+    <mergeCell ref="A65"/>
+    <mergeCell ref="B81:B85"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="A104:A109"/>
+    <mergeCell ref="B24:B29"/>
+    <mergeCell ref="A56"/>
+    <mergeCell ref="B86:B90"/>
+    <mergeCell ref="B34:B41"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="B42:B55"/>
+    <mergeCell ref="B66:B80"/>
+    <mergeCell ref="B2:B19"/>
+    <mergeCell ref="B91:B94"/>
+    <mergeCell ref="A86:A90"/>
+    <mergeCell ref="B104:B109"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/verbose/planning-permission-for-relevant-demolition-in-a-conservation-area-demolition-con-area-verbose.xlsx
+++ b/generated/spreadsheet/verbose/planning-permission-for-relevant-demolition-in-a-conservation-area-demolition-con-area-verbose.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N109"/>
+  <dimension ref="A1:N112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -440,9 +440,9 @@
     <col width="29" customWidth="1" min="8" max="8"/>
     <col width="29" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
     <col width="72" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -1980,19 +1980,27 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>address-text</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>Address Text</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2036,19 +2044,27 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>postcode</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2063,88 +2079,104 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>applicants</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Unique Property Reference Number for a property</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Agent contact details</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>agent-contact</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>agent-reference</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Agent reference</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>A reference to an agent object</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>contact-details</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -2154,7 +2186,7 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2178,29 +2210,21 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -2210,7 +2234,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2244,24 +2268,24 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>contact-priority</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2271,16 +2295,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>agent-details</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="2" t="n"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -2288,47 +2304,63 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>contact-priority</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n"/>
-      <c r="B35" s="2" t="n"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>agent-details</t>
+        </is>
+      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -2346,29 +2378,21 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -2378,7 +2402,7 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2412,19 +2436,19 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -2434,7 +2458,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2468,19 +2492,19 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -2524,19 +2548,19 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -2580,19 +2604,27 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>contact-address</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="2" t="inlineStr"/>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -2602,7 +2634,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2626,21 +2658,37 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-      <c r="K40" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -2674,26 +2722,42 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>user-role</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -2703,50 +2767,50 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity net gain</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>bng</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
+          <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>bng-condition-applies</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition applies</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2755,27 +2819,27 @@
       <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
+          <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>bng-condition-exemption-reasons</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition exemption reason[]</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>exemption-type</t>
+          <t>user-role</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Exemption type</t>
+          <t>User role</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
@@ -2784,7 +2848,7 @@
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -2794,13 +2858,21 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="2" t="n"/>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity net gain</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>bng</t>
+        </is>
+      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>How any natural habitats on the development site will be improved by the proposed works.</t>
@@ -2808,36 +2880,28 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>bng-condition-exemption-reasons</t>
+          <t>bng-condition-applies</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition exemption reason[]</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>reason</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Reason</t>
-        </is>
-      </c>
+          <t>Biodiversity gain condition applies</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>The reason the exemption applies to this proposal</t>
+          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -2856,22 +2920,22 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>bng-details</t>
+          <t>bng-condition-exemption-reasons</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity net gain details</t>
+          <t>Biodiversity gain condition exemption reason[]</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>pre-development-date</t>
+          <t>exemption-type</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Pre development date</t>
+          <t>Exemption type</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
@@ -2880,12 +2944,12 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
+          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -2904,22 +2968,22 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>bng-details</t>
+          <t>bng-condition-exemption-reasons</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity net gain details</t>
+          <t>Biodiversity gain condition exemption reason[]</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>pre-development-biodiversity-value</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Pre development biodiversity value</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -2928,12 +2992,12 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
+          <t>The reason the exemption applies to this proposal</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -2962,12 +3026,12 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>earlier-date-reason</t>
+          <t>pre-development-date</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Earlier date reason</t>
+          <t>Pre development date</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -2976,17 +3040,17 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Reason for using a pre-development date that is earlier than the application submission</t>
+          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3074,12 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>habitat-loss-after-2020</t>
+          <t>pre-development-biodiversity-value</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss after 2020</t>
+          <t>Pre development biodiversity value</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
@@ -3024,17 +3088,17 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
+          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3058,39 +3122,31 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>habitat-loss-details</t>
+          <t>earlier-date-reason</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss details</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>loss-date</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>Loss date</t>
-        </is>
-      </c>
+          <t>Earlier date reason</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Date the activity causing habitat loss or degradation occurred</t>
+          <t>Reason for using a pre-development date that is earlier than the application submission</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3114,39 +3170,31 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>habitat-loss-details</t>
+          <t>habitat-loss-after-2020</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss details</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>pre-loss-biodiversity-value</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>Pre loss biodiversity value</t>
-        </is>
-      </c>
+          <t>Habitat loss after 2020</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
+          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3180,29 +3228,29 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>supporting-evidence</t>
+          <t>loss-date</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Supporting evidence</t>
+          <t>Loss date</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
+          <t>Date the activity causing habitat loss or degradation occurred</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3226,26 +3274,34 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>metric-publication-date</t>
+          <t>habitat-loss-details</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Metric publication date</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr"/>
-      <c r="I52" s="2" t="inlineStr"/>
+          <t>Habitat loss details</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>pre-loss-biodiversity-value</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Pre loss biodiversity value</t>
+        </is>
+      </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Publication date of the biodiversity metric tool used for calculations</t>
+          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -3274,31 +3330,39 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>irreplaceable-habitats</t>
+          <t>habitat-loss-details</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr"/>
-      <c r="I53" s="2" t="inlineStr"/>
+          <t>Habitat loss details</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>supporting-evidence</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Supporting evidence</t>
+        </is>
+      </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether the site contains any irreplaceable habitats</t>
+          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3322,12 +3386,12 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>irreplaceable-habitats-details</t>
+          <t>metric-publication-date</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats details</t>
+          <t>Metric publication date</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
@@ -3336,17 +3400,17 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Description and references for any irreplaceable habitats identified on the site</t>
+          <t>Publication date of the biodiversity metric tool used for calculations</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3370,34 +3434,26 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>irreplaceable-habitats</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Irreplaceable habitats</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Indicates whether the site contains any irreplaceable habitats</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -3407,40 +3463,40 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>checklist</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="n"/>
+      <c r="B56" s="2" t="n"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>national-req-types</t>
+          <t>bng-details</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr"/>
-      <c r="G56" s="2" t="inlineStr"/>
+          <t>Biodiversity net gain details</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>irreplaceable-habitats-details</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Irreplaceable habitats details</t>
+        </is>
+      </c>
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Description and references for any irreplaceable habitats identified on the site</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -3450,50 +3506,58 @@
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>Community consultation</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>community-consultation</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="n"/>
+      <c r="B57" s="2" t="n"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>What community consultation activities have taken place as part of the application</t>
+          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>have-consulted</t>
+          <t>bng-details</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Have consulted</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="inlineStr"/>
+          <t>Biodiversity net gain details</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>supporting-documents</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Whether community consultation has been carried out</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -3503,21 +3567,29 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n"/>
-      <c r="B58" s="2" t="n"/>
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>checklist</t>
+        </is>
+      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>What community consultation activities have taken place as part of the application</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>national-req-types</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
@@ -3528,7 +3600,7 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Provide details of the community consultation</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -3538,34 +3610,34 @@
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Conflict of interest</t>
+          <t>Community consultation</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>conflict-of-interest</t>
+          <t>community-consultation</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>What community consultation activities have taken place as part of the application</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>conflict-to-declare</t>
+          <t>have-consulted</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>Have consulted</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
@@ -3576,7 +3648,7 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Whether community consultation has been carried out</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -3595,17 +3667,17 @@
       <c r="B60" s="2" t="n"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>What community consultation activities have taken place as part of the application</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>person-reference</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
@@ -3616,7 +3688,7 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Reference to the applicant or agent with the conflict</t>
+          <t>Provide details of the community consultation</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -3631,8 +3703,16 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n"/>
-      <c r="B61" s="2" t="n"/>
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>conflict-of-interest</t>
+        </is>
+      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
@@ -3640,12 +3720,12 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>conflict-details</t>
+          <t>conflict-to-declare</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
@@ -3656,34 +3736,26 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>declaration</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="n"/>
+      <c r="B62" s="2" t="n"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3704,7 +3776,7 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -3714,7 +3786,7 @@
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3723,17 +3795,17 @@
       <c r="B63" s="2" t="n"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>conflict-details</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr"/>
@@ -3744,23 +3816,31 @@
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n"/>
-      <c r="B64" s="2" t="n"/>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>declaration</t>
+        </is>
+      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>Signed and dated verification of the application's accuracy.</t>
@@ -3768,12 +3848,12 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr"/>
@@ -3784,12 +3864,12 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -3799,29 +3879,21 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Demolition reason</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>demolition-reason</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Why demolition is necessary at the development site</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
@@ -3832,12 +3904,12 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Why is it necessary to demolish all or part of the building(s) and structure(s)?</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -3847,29 +3919,21 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>ownership-certs</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="n"/>
+      <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>sole-owner</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
@@ -3880,12 +3944,12 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -3895,21 +3959,29 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n"/>
-      <c r="B67" s="2" t="n"/>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Demolition reason</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>demolition-reason</t>
+        </is>
+      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Why demolition is necessary at the development site</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>agricultural-tenants</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Agricultural tenants</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
@@ -3920,12 +3992,12 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Are there any agricultural tenants on the land?</t>
+          <t>Why is it necessary to demolish all or part of the building(s) and structure(s)?</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -3935,8 +4007,16 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n"/>
-      <c r="B68" s="2" t="n"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>ownership-certs</t>
+        </is>
+      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
@@ -3944,49 +4024,33 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>owners-and-tenants</t>
+          <t>sole-owner</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Sole owner</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4000,44 +4064,28 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>owners-and-tenants</t>
+          <t>agricultural-tenants</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>first-name</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>First Name</t>
-        </is>
-      </c>
+          <t>Agricultural tenants</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>Are there any agricultural tenants on the land?</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -4076,19 +4124,19 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -4098,7 +4146,7 @@
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4132,19 +4180,19 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -4188,19 +4236,19 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -4210,7 +4258,7 @@
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4234,31 +4282,47 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>notice-served-date</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Notice served date</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr"/>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-      <c r="K73" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4272,28 +4336,52 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>ownership-cert-option</t>
+          <t>owners-and-tenants</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr"/>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr"/>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-      <c r="K74" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -4312,23 +4400,47 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>steps-taken</t>
+          <t>owners-and-tenants</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr"/>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr"/>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-      <c r="K75" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -4352,22 +4464,22 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>owners-and-tenants</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
+          <t>Owners and tenants[]</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>newspaper-name</t>
+          <t>notice-served-date</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Newspaper name</t>
+          <t>Notice served date</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
@@ -4376,17 +4488,17 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4400,41 +4512,33 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>ownership-cert-option</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>publication-date</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr"/>
       <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4448,12 +4552,12 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>person-reference</t>
+          <t>steps-taken</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>Steps taken</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
@@ -4464,7 +4568,7 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -4474,7 +4578,7 @@
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4488,28 +4592,36 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr"/>
-      <c r="G79" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>newspaper-name</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="H79" s="2" t="inlineStr"/>
       <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -4528,23 +4640,31 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>publication-date</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Publication date</t>
+        </is>
+      </c>
       <c r="H80" s="2" t="inlineStr"/>
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -4559,29 +4679,21 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>pre-app-advice</t>
-        </is>
-      </c>
+      <c r="A81" s="2" t="n"/>
+      <c r="B81" s="2" t="n"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>advice-sought</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr"/>
@@ -4592,12 +4704,12 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -4611,17 +4723,17 @@
       <c r="B82" s="2" t="n"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>officer-name</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
@@ -4632,17 +4744,17 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4651,17 +4763,17 @@
       <c r="B83" s="2" t="n"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr"/>
@@ -4672,23 +4784,31 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n"/>
-      <c r="B84" s="2" t="n"/>
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>pre-app-advice</t>
+        </is>
+      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>Details of pre-application advice previously received from the planning authority</t>
@@ -4696,12 +4816,12 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>advice-date</t>
+          <t>advice-sought</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr"/>
@@ -4712,17 +4832,17 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4736,12 +4856,12 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>advice-summary</t>
+          <t>officer-name</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr"/>
@@ -4752,7 +4872,7 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -4767,29 +4887,21 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>proposal-details</t>
-        </is>
-      </c>
+      <c r="A86" s="2" t="n"/>
+      <c r="B86" s="2" t="n"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>What development, works or change of use is proposed</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
@@ -4800,7 +4912,7 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -4810,7 +4922,7 @@
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4819,17 +4931,17 @@
       <c r="B87" s="2" t="n"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>What development, works or change of use is proposed</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>proposal-started</t>
+          <t>advice-date</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
@@ -4840,17 +4952,17 @@
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4859,17 +4971,17 @@
       <c r="B88" s="2" t="n"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>What development, works or change of use is proposed</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>proposal-started-date</t>
+          <t>advice-summary</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr"/>
@@ -4880,12 +4992,12 @@
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -4895,8 +5007,16 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n"/>
-      <c r="B89" s="2" t="n"/>
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>proposal-details</t>
+        </is>
+      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>What development, works or change of use is proposed</t>
@@ -4904,12 +5024,12 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal description</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr"/>
@@ -4920,12 +5040,12 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -4944,12 +5064,12 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed-date</t>
+          <t>proposal-started</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
@@ -4960,44 +5080,36 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>Related applications</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>related-applications</t>
-        </is>
-      </c>
+      <c r="A91" s="2" t="n"/>
+      <c r="B91" s="2" t="n"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Details of any other development proposals made for the site</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>has-related-applications</t>
+          <t>proposal-started-date</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Has related applications</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr"/>
@@ -5008,17 +5120,17 @@
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>Are there any related applications, previous proposals or demolitions for the site</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5027,41 +5139,33 @@
       <c r="B92" s="2" t="n"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Details of any other development proposals made for the site</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>related-applications</t>
+          <t>proposal-completed</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Related applications[]</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Proposal completed</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr"/>
       <c r="I92" s="2" t="inlineStr"/>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>The reference for the related application</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -5075,52 +5179,52 @@
       <c r="B93" s="2" t="n"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Details of any other development proposals made for the site</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>related-applications</t>
+          <t>proposal-completed-date</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Related applications[]</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
+          <t>Proposal completion date</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr"/>
       <c r="H93" s="2" t="inlineStr"/>
       <c r="I93" s="2" t="inlineStr"/>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>A description of the related application</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n"/>
-      <c r="B94" s="2" t="n"/>
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Related applications</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>related-applications</t>
+        </is>
+      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>Details of any other development proposals made for the site</t>
@@ -5128,78 +5232,62 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>related-applications</t>
+          <t>has-related-applications</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Related applications[]</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>decision-date</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>Decision date</t>
-        </is>
-      </c>
+          <t>Has related applications</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr"/>
       <c r="H94" s="2" t="inlineStr"/>
       <c r="I94" s="2" t="inlineStr"/>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>The date when the decision was made, in YYYY-MM-DD format</t>
+          <t>Are there any related applications, previous proposals or demolitions for the site</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A95" s="2" t="n"/>
+      <c r="B95" s="2" t="n"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of any other development proposals made for the site</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>related-applications</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Related applications[]</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>site-boundary</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr"/>
@@ -5208,17 +5296,17 @@
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>The reference for the related application</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5227,27 +5315,27 @@
       <c r="B96" s="2" t="n"/>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of any other development proposals made for the site</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>related-applications</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Related applications[]</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr"/>
@@ -5256,7 +5344,7 @@
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>A description of the related application</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
@@ -5266,7 +5354,7 @@
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5275,27 +5363,27 @@
       <c r="B97" s="2" t="n"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of any other development proposals made for the site</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>related-applications</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Related applications[]</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>decision-date</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Decision date</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr"/>
@@ -5304,12 +5392,12 @@
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The date when the decision was made, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -5319,8 +5407,16 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n"/>
-      <c r="B98" s="2" t="n"/>
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -5338,12 +5434,12 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>easting</t>
+          <t>geometry</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr"/>
@@ -5352,17 +5448,17 @@
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>A polygon or multipolygon boundary</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>multipolygon</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5386,31 +5482,39 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr"/>
-      <c r="I99" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5434,26 +5538,34 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr"/>
-      <c r="I100" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -5482,26 +5594,34 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr"/>
-      <c r="I101" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>uprns</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Unique Property Reference Numbers (UPRNs) for existing premises within a site boundary</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -5530,21 +5650,29 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr"/>
-      <c r="I102" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>usrns</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>USRNs[]</t>
+        </is>
+      </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject.</t>
+          <t>Unique Street Reference Numbers (USRNs) associated with the site</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
@@ -5578,12 +5706,12 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>uprns</t>
+          <t>easting</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr"/>
@@ -5592,12 +5720,12 @@
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -5607,50 +5735,50 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>site-visit</t>
-        </is>
-      </c>
+      <c r="A104" s="2" t="n"/>
+      <c r="B104" s="2" t="n"/>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>can-be-seen-from</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr"/>
-      <c r="G104" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>northing</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Northing</t>
+        </is>
+      </c>
       <c r="H104" s="2" t="inlineStr"/>
       <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5659,38 +5787,46 @@
       <c r="B105" s="2" t="n"/>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>contact-type</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr"/>
-      <c r="G105" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
       <c r="H105" s="2" t="inlineStr"/>
       <c r="I105" s="2" t="inlineStr"/>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5699,33 +5835,41 @@
       <c r="B106" s="2" t="n"/>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>contact-reference</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr"/>
-      <c r="G106" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
       <c r="H106" s="2" t="inlineStr"/>
       <c r="I106" s="2" t="inlineStr"/>
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -5735,8 +5879,16 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n"/>
-      <c r="B107" s="2" t="n"/>
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>site-visit</t>
+        </is>
+      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>Information to help the planning authority arrange a site visit</t>
@@ -5744,36 +5896,28 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>can-be-seen-from</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>fullname</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>Full name</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr"/>
       <c r="H107" s="2" t="inlineStr"/>
       <c r="I107" s="2" t="inlineStr"/>
       <c r="J107" s="2" t="inlineStr"/>
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -5792,36 +5936,28 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>contact-type</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Site visit contact type</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr"/>
       <c r="I108" s="2" t="inlineStr"/>
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -5840,39 +5976,175 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>contact-reference</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr"/>
       <c r="I109" s="2" t="inlineStr"/>
       <c r="J109" s="2" t="inlineStr"/>
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n"/>
+      <c r="B110" s="2" t="n"/>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>other-contact</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>fullname</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>The complete name of a person</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n"/>
+      <c r="B111" s="2" t="n"/>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>other-contact</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr"/>
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr"/>
+      <c r="K111" s="2" t="inlineStr"/>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>A phone number</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n"/>
+      <c r="B112" s="2" t="n"/>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>other-contact</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr"/>
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr"/>
+      <c r="K112" s="2" t="inlineStr"/>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
           <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
-      <c r="M109" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N109" s="2" t="inlineStr">
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -5880,40 +6152,40 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="B65"/>
-    <mergeCell ref="A34:A41"/>
-    <mergeCell ref="A42:A55"/>
-    <mergeCell ref="A24:A29"/>
+    <mergeCell ref="B44:B57"/>
+    <mergeCell ref="A107:A112"/>
+    <mergeCell ref="B31:B34"/>
+    <mergeCell ref="B84:B88"/>
+    <mergeCell ref="A94:A97"/>
+    <mergeCell ref="B94:B97"/>
+    <mergeCell ref="B98:B106"/>
     <mergeCell ref="A2:A19"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A95:A103"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="A66:A80"/>
-    <mergeCell ref="A81:A85"/>
-    <mergeCell ref="B95:B103"/>
-    <mergeCell ref="B59:B61"/>
-    <mergeCell ref="B62:B64"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="B56"/>
-    <mergeCell ref="A91:A94"/>
-    <mergeCell ref="A65"/>
-    <mergeCell ref="B81:B85"/>
+    <mergeCell ref="B68:B83"/>
+    <mergeCell ref="A67"/>
+    <mergeCell ref="A44:A57"/>
+    <mergeCell ref="A58"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="B24:B30"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="B89:B93"/>
+    <mergeCell ref="A68:A83"/>
+    <mergeCell ref="B107:B112"/>
+    <mergeCell ref="A35:A43"/>
+    <mergeCell ref="B58"/>
     <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="A104:A109"/>
-    <mergeCell ref="B24:B29"/>
-    <mergeCell ref="A56"/>
-    <mergeCell ref="B86:B90"/>
-    <mergeCell ref="B34:B41"/>
+    <mergeCell ref="A24:A30"/>
+    <mergeCell ref="A61:A63"/>
+    <mergeCell ref="B35:B43"/>
+    <mergeCell ref="B67"/>
+    <mergeCell ref="A98:A106"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="A84:A88"/>
+    <mergeCell ref="A31:A34"/>
     <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B42:B55"/>
-    <mergeCell ref="B66:B80"/>
+    <mergeCell ref="A59:A60"/>
     <mergeCell ref="B2:B19"/>
-    <mergeCell ref="B91:B94"/>
-    <mergeCell ref="A86:A90"/>
-    <mergeCell ref="B104:B109"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="A89:A93"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
